--- a/backend/temp/DEBUG_Autofill_2026학년도 신입생 최종 모집결과(대동대학교)-입력요청.xlsx
+++ b/backend/temp/DEBUG_Autofill_2026학년도 신입생 최종 모집결과(대동대학교)-입력요청.xlsx
@@ -1281,49 +1281,135 @@
           <t>주간</t>
         </is>
       </c>
-      <c r="F5" s="8" t="n"/>
-      <c r="G5" s="8" t="n"/>
-      <c r="H5" s="9" t="n"/>
-      <c r="I5" s="9" t="n"/>
-      <c r="J5" s="9" t="n"/>
-      <c r="K5" s="8" t="n"/>
-      <c r="L5" s="9" t="n"/>
-      <c r="M5" s="9" t="n"/>
-      <c r="N5" s="9" t="n"/>
-      <c r="O5" s="8" t="n"/>
-      <c r="P5" s="9" t="n"/>
-      <c r="Q5" s="9" t="n"/>
-      <c r="R5" s="9" t="n"/>
-      <c r="S5" s="8" t="n"/>
-      <c r="T5" s="9" t="n"/>
-      <c r="U5" s="9" t="n"/>
-      <c r="V5" s="9" t="n"/>
-      <c r="W5" s="8" t="n"/>
-      <c r="X5" s="9" t="n"/>
-      <c r="Y5" s="9" t="n"/>
-      <c r="Z5" s="9" t="n"/>
-      <c r="AA5" s="8" t="n"/>
-      <c r="AB5" s="9" t="n"/>
-      <c r="AC5" s="9" t="n"/>
-      <c r="AD5" s="9" t="n"/>
-      <c r="AE5" s="8" t="n"/>
-      <c r="AF5" s="9" t="n"/>
-      <c r="AG5" s="9" t="n"/>
-      <c r="AH5" s="9" t="n"/>
-      <c r="AI5" s="8" t="n"/>
-      <c r="AJ5" s="9" t="n"/>
-      <c r="AK5" s="9" t="n"/>
-      <c r="AL5" s="9" t="n"/>
-      <c r="AM5" s="8" t="n"/>
-      <c r="AN5" s="9" t="n"/>
-      <c r="AO5" s="9" t="n"/>
-      <c r="AP5" s="9" t="n"/>
-      <c r="AQ5" s="8" t="n"/>
-      <c r="AR5" s="8" t="n"/>
-      <c r="AS5" s="8" t="n"/>
-      <c r="AT5" s="33" t="n"/>
-      <c r="AU5" s="10" t="n"/>
-      <c r="AV5" s="11" t="n"/>
+      <c r="F5" s="8" t="n">
+        <v>230</v>
+      </c>
+      <c r="G5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K5" s="8" t="n">
+        <v>209</v>
+      </c>
+      <c r="L5" s="9" t="n">
+        <v>209</v>
+      </c>
+      <c r="M5" s="9" t="n">
+        <v>1846</v>
+      </c>
+      <c r="N5" s="9" t="n">
+        <v>202</v>
+      </c>
+      <c r="O5" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P5" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q5" s="9" t="n">
+        <v>434</v>
+      </c>
+      <c r="R5" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="S5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM5" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN5" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO5" s="9" t="n">
+        <v>300</v>
+      </c>
+      <c r="AP5" s="9" t="n">
+        <v>17</v>
+      </c>
+      <c r="AQ5" s="8" t="n">
+        <v>220</v>
+      </c>
+      <c r="AR5" s="8" t="n">
+        <v>2580</v>
+      </c>
+      <c r="AS5" s="8" t="n">
+        <v>230</v>
+      </c>
+      <c r="AT5" s="33" t="n">
+        <v>11.73</v>
+      </c>
+      <c r="AU5" s="10" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="AV5" s="11" t="n">
+        <v>-10</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="n"/>
@@ -1335,49 +1421,135 @@
           <t>야간</t>
         </is>
       </c>
-      <c r="F6" s="8" t="n"/>
-      <c r="G6" s="8" t="n"/>
-      <c r="H6" s="9" t="n"/>
-      <c r="I6" s="9" t="n"/>
-      <c r="J6" s="9" t="n"/>
-      <c r="K6" s="8" t="n"/>
-      <c r="L6" s="9" t="n"/>
-      <c r="M6" s="9" t="n"/>
-      <c r="N6" s="9" t="n"/>
-      <c r="O6" s="8" t="n"/>
-      <c r="P6" s="9" t="n"/>
-      <c r="Q6" s="9" t="n"/>
-      <c r="R6" s="9" t="n"/>
-      <c r="S6" s="8" t="n"/>
-      <c r="T6" s="9" t="n"/>
-      <c r="U6" s="9" t="n"/>
-      <c r="V6" s="9" t="n"/>
-      <c r="W6" s="8" t="n"/>
-      <c r="X6" s="9" t="n"/>
-      <c r="Y6" s="9" t="n"/>
-      <c r="Z6" s="9" t="n"/>
-      <c r="AA6" s="8" t="n"/>
-      <c r="AB6" s="9" t="n"/>
-      <c r="AC6" s="9" t="n"/>
-      <c r="AD6" s="9" t="n"/>
-      <c r="AE6" s="8" t="n"/>
-      <c r="AF6" s="9" t="n"/>
-      <c r="AG6" s="9" t="n"/>
-      <c r="AH6" s="9" t="n"/>
-      <c r="AI6" s="8" t="n"/>
-      <c r="AJ6" s="9" t="n"/>
-      <c r="AK6" s="9" t="n"/>
-      <c r="AL6" s="9" t="n"/>
-      <c r="AM6" s="8" t="n"/>
-      <c r="AN6" s="9" t="n"/>
-      <c r="AO6" s="9" t="n"/>
-      <c r="AP6" s="9" t="n"/>
-      <c r="AQ6" s="8" t="n"/>
-      <c r="AR6" s="8" t="n"/>
-      <c r="AS6" s="8" t="n"/>
-      <c r="AT6" s="10" t="n"/>
-      <c r="AU6" s="10" t="n"/>
-      <c r="AV6" s="11" t="n"/>
+      <c r="F6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP6" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS6" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU6" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV6" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="n"/>
@@ -1401,49 +1573,135 @@
           <t>주간</t>
         </is>
       </c>
-      <c r="F7" s="8" t="n"/>
-      <c r="G7" s="8" t="n"/>
-      <c r="H7" s="9" t="n"/>
-      <c r="I7" s="9" t="n"/>
-      <c r="J7" s="9" t="n"/>
-      <c r="K7" s="8" t="n"/>
-      <c r="L7" s="9" t="n"/>
-      <c r="M7" s="9" t="n"/>
-      <c r="N7" s="9" t="n"/>
-      <c r="O7" s="8" t="n"/>
-      <c r="P7" s="9" t="n"/>
-      <c r="Q7" s="9" t="n"/>
-      <c r="R7" s="9" t="n"/>
-      <c r="S7" s="8" t="n"/>
-      <c r="T7" s="9" t="n"/>
-      <c r="U7" s="9" t="n"/>
-      <c r="V7" s="9" t="n"/>
-      <c r="W7" s="8" t="n"/>
-      <c r="X7" s="9" t="n"/>
-      <c r="Y7" s="9" t="n"/>
-      <c r="Z7" s="9" t="n"/>
-      <c r="AA7" s="8" t="n"/>
-      <c r="AB7" s="9" t="n"/>
-      <c r="AC7" s="9" t="n"/>
-      <c r="AD7" s="9" t="n"/>
-      <c r="AE7" s="8" t="n"/>
-      <c r="AF7" s="9" t="n"/>
-      <c r="AG7" s="9" t="n"/>
-      <c r="AH7" s="9" t="n"/>
-      <c r="AI7" s="8" t="n"/>
-      <c r="AJ7" s="9" t="n"/>
-      <c r="AK7" s="9" t="n"/>
-      <c r="AL7" s="9" t="n"/>
-      <c r="AM7" s="8" t="n"/>
-      <c r="AN7" s="9" t="n"/>
-      <c r="AO7" s="9" t="n"/>
-      <c r="AP7" s="9" t="n"/>
-      <c r="AQ7" s="8" t="n"/>
-      <c r="AR7" s="8" t="n"/>
-      <c r="AS7" s="8" t="n"/>
-      <c r="AT7" s="33" t="n"/>
-      <c r="AU7" s="10" t="n"/>
-      <c r="AV7" s="11" t="n"/>
+      <c r="F7" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="G7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="L7" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="M7" s="9" t="n">
+        <v>247</v>
+      </c>
+      <c r="N7" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="O7" s="8" t="n">
+        <v>7</v>
+      </c>
+      <c r="P7" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="Q7" s="9" t="n">
+        <v>131</v>
+      </c>
+      <c r="R7" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="S7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI7" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM7" s="8" t="n">
+        <v>9</v>
+      </c>
+      <c r="AN7" s="9" t="n">
+        <v>9</v>
+      </c>
+      <c r="AO7" s="9" t="n">
+        <v>26</v>
+      </c>
+      <c r="AP7" s="9" t="n">
+        <v>7</v>
+      </c>
+      <c r="AQ7" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AR7" s="8" t="n">
+        <v>404</v>
+      </c>
+      <c r="AS7" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AT7" s="33" t="n">
+        <v>13.47</v>
+      </c>
+      <c r="AU7" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV7" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="n"/>
@@ -1455,49 +1713,135 @@
           <t>야간</t>
         </is>
       </c>
-      <c r="F8" s="8" t="n"/>
-      <c r="G8" s="8" t="n"/>
-      <c r="H8" s="9" t="n"/>
-      <c r="I8" s="9" t="n"/>
-      <c r="J8" s="9" t="n"/>
-      <c r="K8" s="8" t="n"/>
-      <c r="L8" s="9" t="n"/>
-      <c r="M8" s="9" t="n"/>
-      <c r="N8" s="9" t="n"/>
-      <c r="O8" s="8" t="n"/>
-      <c r="P8" s="9" t="n"/>
-      <c r="Q8" s="9" t="n"/>
-      <c r="R8" s="9" t="n"/>
-      <c r="S8" s="8" t="n"/>
-      <c r="T8" s="9" t="n"/>
-      <c r="U8" s="9" t="n"/>
-      <c r="V8" s="9" t="n"/>
-      <c r="W8" s="8" t="n"/>
-      <c r="X8" s="9" t="n"/>
-      <c r="Y8" s="9" t="n"/>
-      <c r="Z8" s="9" t="n"/>
-      <c r="AA8" s="8" t="n"/>
-      <c r="AB8" s="9" t="n"/>
-      <c r="AC8" s="9" t="n"/>
-      <c r="AD8" s="9" t="n"/>
-      <c r="AE8" s="8" t="n"/>
-      <c r="AF8" s="9" t="n"/>
-      <c r="AG8" s="9" t="n"/>
-      <c r="AH8" s="9" t="n"/>
-      <c r="AI8" s="8" t="n"/>
-      <c r="AJ8" s="9" t="n"/>
-      <c r="AK8" s="9" t="n"/>
-      <c r="AL8" s="9" t="n"/>
-      <c r="AM8" s="8" t="n"/>
-      <c r="AN8" s="9" t="n"/>
-      <c r="AO8" s="9" t="n"/>
-      <c r="AP8" s="9" t="n"/>
-      <c r="AQ8" s="8" t="n"/>
-      <c r="AR8" s="8" t="n"/>
-      <c r="AS8" s="8" t="n"/>
-      <c r="AT8" s="10" t="n"/>
-      <c r="AU8" s="10" t="n"/>
-      <c r="AV8" s="11" t="n"/>
+      <c r="F8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP8" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS8" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU8" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV8" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="n"/>
@@ -1521,49 +1865,135 @@
           <t>주간</t>
         </is>
       </c>
-      <c r="F9" s="8" t="n"/>
-      <c r="G9" s="8" t="n"/>
-      <c r="H9" s="9" t="n"/>
-      <c r="I9" s="9" t="n"/>
-      <c r="J9" s="9" t="n"/>
-      <c r="K9" s="8" t="n"/>
-      <c r="L9" s="9" t="n"/>
-      <c r="M9" s="9" t="n"/>
-      <c r="N9" s="9" t="n"/>
-      <c r="O9" s="8" t="n"/>
-      <c r="P9" s="9" t="n"/>
-      <c r="Q9" s="9" t="n"/>
-      <c r="R9" s="9" t="n"/>
-      <c r="S9" s="8" t="n"/>
-      <c r="T9" s="9" t="n"/>
-      <c r="U9" s="9" t="n"/>
-      <c r="V9" s="9" t="n"/>
-      <c r="W9" s="8" t="n"/>
-      <c r="X9" s="9" t="n"/>
-      <c r="Y9" s="9" t="n"/>
-      <c r="Z9" s="9" t="n"/>
-      <c r="AA9" s="8" t="n"/>
-      <c r="AB9" s="9" t="n"/>
-      <c r="AC9" s="9" t="n"/>
-      <c r="AD9" s="9" t="n"/>
-      <c r="AE9" s="8" t="n"/>
-      <c r="AF9" s="9" t="n"/>
-      <c r="AG9" s="9" t="n"/>
-      <c r="AH9" s="9" t="n"/>
-      <c r="AI9" s="8" t="n"/>
-      <c r="AJ9" s="9" t="n"/>
-      <c r="AK9" s="9" t="n"/>
-      <c r="AL9" s="9" t="n"/>
-      <c r="AM9" s="8" t="n"/>
-      <c r="AN9" s="9" t="n"/>
-      <c r="AO9" s="9" t="n"/>
-      <c r="AP9" s="9" t="n"/>
-      <c r="AQ9" s="8" t="n"/>
-      <c r="AR9" s="8" t="n"/>
-      <c r="AS9" s="8" t="n"/>
-      <c r="AT9" s="10" t="n"/>
-      <c r="AU9" s="10" t="n"/>
-      <c r="AV9" s="11" t="n"/>
+      <c r="F9" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M9" s="9" t="n">
+        <v>164</v>
+      </c>
+      <c r="N9" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="O9" s="8" t="n">
+        <v>11</v>
+      </c>
+      <c r="P9" s="9" t="n">
+        <v>11</v>
+      </c>
+      <c r="Q9" s="9" t="n">
+        <v>115</v>
+      </c>
+      <c r="R9" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="S9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL9" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM9" s="8" t="n">
+        <v>4</v>
+      </c>
+      <c r="AN9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO9" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP9" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AQ9" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR9" s="8" t="n">
+        <v>300</v>
+      </c>
+      <c r="AS9" s="8" t="n">
+        <v>19</v>
+      </c>
+      <c r="AT9" s="10" t="n">
+        <v>15</v>
+      </c>
+      <c r="AU9" s="10" t="n">
+        <v>0.95</v>
+      </c>
+      <c r="AV9" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="n"/>
@@ -1575,49 +2005,135 @@
           <t>야간</t>
         </is>
       </c>
-      <c r="F10" s="8" t="n"/>
-      <c r="G10" s="8" t="n"/>
-      <c r="H10" s="9" t="n"/>
-      <c r="I10" s="9" t="n"/>
-      <c r="J10" s="9" t="n"/>
-      <c r="K10" s="8" t="n"/>
-      <c r="L10" s="9" t="n"/>
-      <c r="M10" s="9" t="n"/>
-      <c r="N10" s="9" t="n"/>
-      <c r="O10" s="8" t="n"/>
-      <c r="P10" s="9" t="n"/>
-      <c r="Q10" s="9" t="n"/>
-      <c r="R10" s="9" t="n"/>
-      <c r="S10" s="8" t="n"/>
-      <c r="T10" s="9" t="n"/>
-      <c r="U10" s="9" t="n"/>
-      <c r="V10" s="9" t="n"/>
-      <c r="W10" s="8" t="n"/>
-      <c r="X10" s="9" t="n"/>
-      <c r="Y10" s="9" t="n"/>
-      <c r="Z10" s="9" t="n"/>
-      <c r="AA10" s="8" t="n"/>
-      <c r="AB10" s="9" t="n"/>
-      <c r="AC10" s="9" t="n"/>
-      <c r="AD10" s="9" t="n"/>
-      <c r="AE10" s="8" t="n"/>
-      <c r="AF10" s="9" t="n"/>
-      <c r="AG10" s="9" t="n"/>
-      <c r="AH10" s="9" t="n"/>
-      <c r="AI10" s="8" t="n"/>
-      <c r="AJ10" s="9" t="n"/>
-      <c r="AK10" s="9" t="n"/>
-      <c r="AL10" s="9" t="n"/>
-      <c r="AM10" s="8" t="n"/>
-      <c r="AN10" s="9" t="n"/>
-      <c r="AO10" s="9" t="n"/>
-      <c r="AP10" s="9" t="n"/>
-      <c r="AQ10" s="8" t="n"/>
-      <c r="AR10" s="8" t="n"/>
-      <c r="AS10" s="8" t="n"/>
-      <c r="AT10" s="10" t="n"/>
-      <c r="AU10" s="10" t="n"/>
-      <c r="AV10" s="11" t="n"/>
+      <c r="F10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP10" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS10" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU10" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV10" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="n"/>
@@ -1641,49 +2157,135 @@
           <t>주간</t>
         </is>
       </c>
-      <c r="F11" s="8" t="n"/>
-      <c r="G11" s="8" t="n"/>
-      <c r="H11" s="9" t="n"/>
-      <c r="I11" s="9" t="n"/>
-      <c r="J11" s="9" t="n"/>
-      <c r="K11" s="8" t="n"/>
-      <c r="L11" s="9" t="n"/>
-      <c r="M11" s="9" t="n"/>
-      <c r="N11" s="9" t="n"/>
-      <c r="O11" s="8" t="n"/>
-      <c r="P11" s="9" t="n"/>
-      <c r="Q11" s="9" t="n"/>
-      <c r="R11" s="9" t="n"/>
-      <c r="S11" s="8" t="n"/>
-      <c r="T11" s="9" t="n"/>
-      <c r="U11" s="9" t="n"/>
-      <c r="V11" s="9" t="n"/>
-      <c r="W11" s="8" t="n"/>
-      <c r="X11" s="9" t="n"/>
-      <c r="Y11" s="9" t="n"/>
-      <c r="Z11" s="9" t="n"/>
-      <c r="AA11" s="8" t="n"/>
-      <c r="AB11" s="9" t="n"/>
-      <c r="AC11" s="9" t="n"/>
-      <c r="AD11" s="9" t="n"/>
-      <c r="AE11" s="8" t="n"/>
-      <c r="AF11" s="9" t="n"/>
-      <c r="AG11" s="9" t="n"/>
-      <c r="AH11" s="9" t="n"/>
-      <c r="AI11" s="8" t="n"/>
-      <c r="AJ11" s="9" t="n"/>
-      <c r="AK11" s="9" t="n"/>
-      <c r="AL11" s="9" t="n"/>
-      <c r="AM11" s="8" t="n"/>
-      <c r="AN11" s="9" t="n"/>
-      <c r="AO11" s="9" t="n"/>
-      <c r="AP11" s="9" t="n"/>
-      <c r="AQ11" s="8" t="n"/>
-      <c r="AR11" s="8" t="n"/>
-      <c r="AS11" s="8" t="n"/>
-      <c r="AT11" s="33" t="n"/>
-      <c r="AU11" s="10" t="n"/>
-      <c r="AV11" s="11" t="n"/>
+      <c r="F11" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="G11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="L11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="N11" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="O11" s="8" t="n">
+        <v>3</v>
+      </c>
+      <c r="P11" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="Q11" s="9" t="n">
+        <v>44</v>
+      </c>
+      <c r="R11" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="S11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL11" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM11" s="8" t="n">
+        <v>12</v>
+      </c>
+      <c r="AN11" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AO11" s="9" t="n">
+        <v>75</v>
+      </c>
+      <c r="AP11" s="9" t="n">
+        <v>12</v>
+      </c>
+      <c r="AQ11" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR11" s="8" t="n">
+        <v>194</v>
+      </c>
+      <c r="AS11" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT11" s="33" t="n">
+        <v>10.78</v>
+      </c>
+      <c r="AU11" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV11" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="n"/>
@@ -1695,49 +2297,135 @@
           <t>야간</t>
         </is>
       </c>
-      <c r="F12" s="8" t="n"/>
-      <c r="G12" s="8" t="n"/>
-      <c r="H12" s="9" t="n"/>
-      <c r="I12" s="9" t="n"/>
-      <c r="J12" s="9" t="n"/>
-      <c r="K12" s="8" t="n"/>
-      <c r="L12" s="9" t="n"/>
-      <c r="M12" s="9" t="n"/>
-      <c r="N12" s="9" t="n"/>
-      <c r="O12" s="8" t="n"/>
-      <c r="P12" s="9" t="n"/>
-      <c r="Q12" s="9" t="n"/>
-      <c r="R12" s="9" t="n"/>
-      <c r="S12" s="8" t="n"/>
-      <c r="T12" s="9" t="n"/>
-      <c r="U12" s="9" t="n"/>
-      <c r="V12" s="9" t="n"/>
-      <c r="W12" s="8" t="n"/>
-      <c r="X12" s="9" t="n"/>
-      <c r="Y12" s="9" t="n"/>
-      <c r="Z12" s="9" t="n"/>
-      <c r="AA12" s="8" t="n"/>
-      <c r="AB12" s="9" t="n"/>
-      <c r="AC12" s="9" t="n"/>
-      <c r="AD12" s="9" t="n"/>
-      <c r="AE12" s="8" t="n"/>
-      <c r="AF12" s="9" t="n"/>
-      <c r="AG12" s="9" t="n"/>
-      <c r="AH12" s="9" t="n"/>
-      <c r="AI12" s="8" t="n"/>
-      <c r="AJ12" s="9" t="n"/>
-      <c r="AK12" s="9" t="n"/>
-      <c r="AL12" s="9" t="n"/>
-      <c r="AM12" s="8" t="n"/>
-      <c r="AN12" s="9" t="n"/>
-      <c r="AO12" s="9" t="n"/>
-      <c r="AP12" s="9" t="n"/>
-      <c r="AQ12" s="8" t="n"/>
-      <c r="AR12" s="8" t="n"/>
-      <c r="AS12" s="8" t="n"/>
-      <c r="AT12" s="10" t="n"/>
-      <c r="AU12" s="10" t="n"/>
-      <c r="AV12" s="11" t="n"/>
+      <c r="F12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP12" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS12" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU12" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV12" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="13" ht="24" customHeight="1">
       <c r="A13" s="5" t="n"/>
@@ -1761,49 +2449,135 @@
           <t>주간</t>
         </is>
       </c>
-      <c r="F13" s="8" t="n"/>
-      <c r="G13" s="8" t="n"/>
-      <c r="H13" s="9" t="n"/>
-      <c r="I13" s="9" t="n"/>
-      <c r="J13" s="9" t="n"/>
-      <c r="K13" s="8" t="n"/>
-      <c r="L13" s="9" t="n"/>
-      <c r="M13" s="9" t="n"/>
-      <c r="N13" s="9" t="n"/>
-      <c r="O13" s="8" t="n"/>
-      <c r="P13" s="9" t="n"/>
-      <c r="Q13" s="9" t="n"/>
-      <c r="R13" s="9" t="n"/>
-      <c r="S13" s="8" t="n"/>
-      <c r="T13" s="9" t="n"/>
-      <c r="U13" s="9" t="n"/>
-      <c r="V13" s="9" t="n"/>
-      <c r="W13" s="8" t="n"/>
-      <c r="X13" s="9" t="n"/>
-      <c r="Y13" s="9" t="n"/>
-      <c r="Z13" s="9" t="n"/>
-      <c r="AA13" s="8" t="n"/>
-      <c r="AB13" s="9" t="n"/>
-      <c r="AC13" s="9" t="n"/>
-      <c r="AD13" s="9" t="n"/>
-      <c r="AE13" s="8" t="n"/>
-      <c r="AF13" s="9" t="n"/>
-      <c r="AG13" s="9" t="n"/>
-      <c r="AH13" s="9" t="n"/>
-      <c r="AI13" s="8" t="n"/>
-      <c r="AJ13" s="9" t="n"/>
-      <c r="AK13" s="9" t="n"/>
-      <c r="AL13" s="9" t="n"/>
-      <c r="AM13" s="8" t="n"/>
-      <c r="AN13" s="9" t="n"/>
-      <c r="AO13" s="9" t="n"/>
-      <c r="AP13" s="9" t="n"/>
-      <c r="AQ13" s="8" t="n"/>
-      <c r="AR13" s="8" t="n"/>
-      <c r="AS13" s="8" t="n"/>
-      <c r="AT13" s="33" t="n"/>
-      <c r="AU13" s="10" t="n"/>
-      <c r="AV13" s="11" t="n"/>
+      <c r="F13" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="G13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="L13" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="M13" s="9" t="n">
+        <v>41</v>
+      </c>
+      <c r="N13" s="9" t="n">
+        <v>6</v>
+      </c>
+      <c r="O13" s="8" t="n">
+        <v>5</v>
+      </c>
+      <c r="P13" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q13" s="9" t="n">
+        <v>35</v>
+      </c>
+      <c r="R13" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="S13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL13" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM13" s="8" t="n">
+        <v>8</v>
+      </c>
+      <c r="AN13" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AO13" s="9" t="n">
+        <v>21</v>
+      </c>
+      <c r="AP13" s="9" t="n">
+        <v>8</v>
+      </c>
+      <c r="AQ13" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AR13" s="8" t="n">
+        <v>97</v>
+      </c>
+      <c r="AS13" s="8" t="n">
+        <v>18</v>
+      </c>
+      <c r="AT13" s="33" t="n">
+        <v>5.39</v>
+      </c>
+      <c r="AU13" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV13" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="5" t="n"/>
@@ -1815,49 +2589,135 @@
           <t>야간</t>
         </is>
       </c>
-      <c r="F14" s="8" t="n"/>
-      <c r="G14" s="8" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="9" t="n"/>
-      <c r="K14" s="8" t="n"/>
-      <c r="L14" s="9" t="n"/>
-      <c r="M14" s="9" t="n"/>
-      <c r="N14" s="9" t="n"/>
-      <c r="O14" s="8" t="n"/>
-      <c r="P14" s="9" t="n"/>
-      <c r="Q14" s="9" t="n"/>
-      <c r="R14" s="9" t="n"/>
-      <c r="S14" s="8" t="n"/>
-      <c r="T14" s="9" t="n"/>
-      <c r="U14" s="9" t="n"/>
-      <c r="V14" s="9" t="n"/>
-      <c r="W14" s="8" t="n"/>
-      <c r="X14" s="9" t="n"/>
-      <c r="Y14" s="9" t="n"/>
-      <c r="Z14" s="9" t="n"/>
-      <c r="AA14" s="8" t="n"/>
-      <c r="AB14" s="9" t="n"/>
-      <c r="AC14" s="9" t="n"/>
-      <c r="AD14" s="9" t="n"/>
-      <c r="AE14" s="8" t="n"/>
-      <c r="AF14" s="9" t="n"/>
-      <c r="AG14" s="9" t="n"/>
-      <c r="AH14" s="9" t="n"/>
-      <c r="AI14" s="8" t="n"/>
-      <c r="AJ14" s="9" t="n"/>
-      <c r="AK14" s="9" t="n"/>
-      <c r="AL14" s="9" t="n"/>
-      <c r="AM14" s="8" t="n"/>
-      <c r="AN14" s="9" t="n"/>
-      <c r="AO14" s="9" t="n"/>
-      <c r="AP14" s="9" t="n"/>
-      <c r="AQ14" s="8" t="n"/>
-      <c r="AR14" s="8" t="n"/>
-      <c r="AS14" s="8" t="n"/>
-      <c r="AT14" s="10" t="n"/>
-      <c r="AU14" s="10" t="n"/>
-      <c r="AV14" s="11" t="n"/>
+      <c r="F14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP14" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS14" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU14" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV14" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="5" t="n"/>
@@ -1881,49 +2741,135 @@
           <t>주간</t>
         </is>
       </c>
-      <c r="F15" s="8" t="n"/>
-      <c r="G15" s="8" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="9" t="n"/>
-      <c r="K15" s="8" t="n"/>
-      <c r="L15" s="9" t="n"/>
-      <c r="M15" s="9" t="n"/>
-      <c r="N15" s="9" t="n"/>
-      <c r="O15" s="8" t="n"/>
-      <c r="P15" s="9" t="n"/>
-      <c r="Q15" s="9" t="n"/>
-      <c r="R15" s="9" t="n"/>
-      <c r="S15" s="8" t="n"/>
-      <c r="T15" s="9" t="n"/>
-      <c r="U15" s="9" t="n"/>
-      <c r="V15" s="9" t="n"/>
-      <c r="W15" s="8" t="n"/>
-      <c r="X15" s="9" t="n"/>
-      <c r="Y15" s="9" t="n"/>
-      <c r="Z15" s="9" t="n"/>
-      <c r="AA15" s="8" t="n"/>
-      <c r="AB15" s="9" t="n"/>
-      <c r="AC15" s="9" t="n"/>
-      <c r="AD15" s="9" t="n"/>
-      <c r="AE15" s="8" t="n"/>
-      <c r="AF15" s="9" t="n"/>
-      <c r="AG15" s="9" t="n"/>
-      <c r="AH15" s="9" t="n"/>
-      <c r="AI15" s="8" t="n"/>
-      <c r="AJ15" s="9" t="n"/>
-      <c r="AK15" s="9" t="n"/>
-      <c r="AL15" s="9" t="n"/>
-      <c r="AM15" s="8" t="n"/>
-      <c r="AN15" s="9" t="n"/>
-      <c r="AO15" s="9" t="n"/>
-      <c r="AP15" s="9" t="n"/>
-      <c r="AQ15" s="8" t="n"/>
-      <c r="AR15" s="8" t="n"/>
-      <c r="AS15" s="8" t="n"/>
-      <c r="AT15" s="33" t="n"/>
-      <c r="AU15" s="10" t="n"/>
-      <c r="AV15" s="11" t="n"/>
+      <c r="F15" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL15" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM15" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN15" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO15" s="9" t="n">
+        <v>47</v>
+      </c>
+      <c r="AP15" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AQ15" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR15" s="8" t="n">
+        <v>47</v>
+      </c>
+      <c r="AS15" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AT15" s="33" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="AU15" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV15" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="12" t="n"/>
@@ -1935,49 +2881,135 @@
           <t>야간</t>
         </is>
       </c>
-      <c r="F16" s="8" t="n"/>
-      <c r="G16" s="8" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="9" t="n"/>
-      <c r="K16" s="8" t="n"/>
-      <c r="L16" s="9" t="n"/>
-      <c r="M16" s="9" t="n"/>
-      <c r="N16" s="9" t="n"/>
-      <c r="O16" s="8" t="n"/>
-      <c r="P16" s="9" t="n"/>
-      <c r="Q16" s="9" t="n"/>
-      <c r="R16" s="9" t="n"/>
-      <c r="S16" s="8" t="n"/>
-      <c r="T16" s="9" t="n"/>
-      <c r="U16" s="9" t="n"/>
-      <c r="V16" s="9" t="n"/>
-      <c r="W16" s="8" t="n"/>
-      <c r="X16" s="9" t="n"/>
-      <c r="Y16" s="9" t="n"/>
-      <c r="Z16" s="9" t="n"/>
-      <c r="AA16" s="8" t="n"/>
-      <c r="AB16" s="9" t="n"/>
-      <c r="AC16" s="9" t="n"/>
-      <c r="AD16" s="9" t="n"/>
-      <c r="AE16" s="8" t="n"/>
-      <c r="AF16" s="9" t="n"/>
-      <c r="AG16" s="9" t="n"/>
-      <c r="AH16" s="9" t="n"/>
-      <c r="AI16" s="8" t="n"/>
-      <c r="AJ16" s="9" t="n"/>
-      <c r="AK16" s="9" t="n"/>
-      <c r="AL16" s="9" t="n"/>
-      <c r="AM16" s="8" t="n"/>
-      <c r="AN16" s="9" t="n"/>
-      <c r="AO16" s="9" t="n"/>
-      <c r="AP16" s="9" t="n"/>
-      <c r="AQ16" s="8" t="n"/>
-      <c r="AR16" s="8" t="n"/>
-      <c r="AS16" s="8" t="n"/>
-      <c r="AT16" s="10" t="n"/>
-      <c r="AU16" s="10" t="n"/>
-      <c r="AV16" s="11" t="n"/>
+      <c r="F16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP16" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS16" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU16" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV16" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="5" t="inlineStr">
@@ -2005,49 +3037,135 @@
           <t>주간</t>
         </is>
       </c>
-      <c r="F17" s="8" t="n"/>
-      <c r="G17" s="8" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="9" t="n"/>
-      <c r="K17" s="8" t="n"/>
-      <c r="L17" s="9" t="n"/>
-      <c r="M17" s="9" t="n"/>
-      <c r="N17" s="9" t="n"/>
-      <c r="O17" s="8" t="n"/>
-      <c r="P17" s="9" t="n"/>
-      <c r="Q17" s="9" t="n"/>
-      <c r="R17" s="9" t="n"/>
-      <c r="S17" s="8" t="n"/>
-      <c r="T17" s="9" t="n"/>
-      <c r="U17" s="9" t="n"/>
-      <c r="V17" s="9" t="n"/>
-      <c r="W17" s="8" t="n"/>
-      <c r="X17" s="9" t="n"/>
-      <c r="Y17" s="9" t="n"/>
-      <c r="Z17" s="9" t="n"/>
-      <c r="AA17" s="8" t="n"/>
-      <c r="AB17" s="9" t="n"/>
-      <c r="AC17" s="9" t="n"/>
-      <c r="AD17" s="9" t="n"/>
-      <c r="AE17" s="8" t="n"/>
-      <c r="AF17" s="9" t="n"/>
-      <c r="AG17" s="9" t="n"/>
-      <c r="AH17" s="9" t="n"/>
-      <c r="AI17" s="8" t="n"/>
-      <c r="AJ17" s="9" t="n"/>
-      <c r="AK17" s="9" t="n"/>
-      <c r="AL17" s="9" t="n"/>
-      <c r="AM17" s="8" t="n"/>
-      <c r="AN17" s="9" t="n"/>
-      <c r="AO17" s="9" t="n"/>
-      <c r="AP17" s="9" t="n"/>
-      <c r="AQ17" s="8" t="n"/>
-      <c r="AR17" s="8" t="n"/>
-      <c r="AS17" s="8" t="n"/>
-      <c r="AT17" s="33" t="n"/>
-      <c r="AU17" s="10" t="n"/>
-      <c r="AV17" s="11" t="n"/>
+      <c r="F17" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="G17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI17" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL17" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM17" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN17" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AO17" s="9" t="n">
+        <v>61</v>
+      </c>
+      <c r="AP17" s="9" t="n">
+        <v>20</v>
+      </c>
+      <c r="AQ17" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AR17" s="8" t="n">
+        <v>61</v>
+      </c>
+      <c r="AS17" s="8" t="n">
+        <v>20</v>
+      </c>
+      <c r="AT17" s="33" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="AU17" s="10" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV17" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="12" t="n"/>
@@ -2059,49 +3177,135 @@
           <t>야간</t>
         </is>
       </c>
-      <c r="F18" s="8" t="n"/>
-      <c r="G18" s="8" t="n"/>
-      <c r="H18" s="9" t="n"/>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="9" t="n"/>
-      <c r="K18" s="8" t="n"/>
-      <c r="L18" s="9" t="n"/>
-      <c r="M18" s="9" t="n"/>
-      <c r="N18" s="9" t="n"/>
-      <c r="O18" s="8" t="n"/>
-      <c r="P18" s="9" t="n"/>
-      <c r="Q18" s="9" t="n"/>
-      <c r="R18" s="9" t="n"/>
-      <c r="S18" s="8" t="n"/>
-      <c r="T18" s="9" t="n"/>
-      <c r="U18" s="9" t="n"/>
-      <c r="V18" s="9" t="n"/>
-      <c r="W18" s="8" t="n"/>
-      <c r="X18" s="9" t="n"/>
-      <c r="Y18" s="9" t="n"/>
-      <c r="Z18" s="9" t="n"/>
-      <c r="AA18" s="8" t="n"/>
-      <c r="AB18" s="9" t="n"/>
-      <c r="AC18" s="9" t="n"/>
-      <c r="AD18" s="9" t="n"/>
-      <c r="AE18" s="8" t="n"/>
-      <c r="AF18" s="9" t="n"/>
-      <c r="AG18" s="9" t="n"/>
-      <c r="AH18" s="9" t="n"/>
-      <c r="AI18" s="8" t="n"/>
-      <c r="AJ18" s="9" t="n"/>
-      <c r="AK18" s="9" t="n"/>
-      <c r="AL18" s="9" t="n"/>
-      <c r="AM18" s="8" t="n"/>
-      <c r="AN18" s="9" t="n"/>
-      <c r="AO18" s="9" t="n"/>
-      <c r="AP18" s="9" t="n"/>
-      <c r="AQ18" s="8" t="n"/>
-      <c r="AR18" s="8" t="n"/>
-      <c r="AS18" s="8" t="n"/>
-      <c r="AT18" s="10" t="n"/>
-      <c r="AU18" s="10" t="n"/>
-      <c r="AV18" s="11" t="n"/>
+      <c r="F18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP18" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU18" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV18" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="5" t="inlineStr">
@@ -2129,49 +3333,135 @@
           <t>주간</t>
         </is>
       </c>
-      <c r="F19" s="8" t="n"/>
-      <c r="G19" s="8" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="9" t="n"/>
-      <c r="K19" s="8" t="n"/>
-      <c r="L19" s="9" t="n"/>
-      <c r="M19" s="9" t="n"/>
-      <c r="N19" s="9" t="n"/>
-      <c r="O19" s="8" t="n"/>
-      <c r="P19" s="9" t="n"/>
-      <c r="Q19" s="9" t="n"/>
-      <c r="R19" s="9" t="n"/>
-      <c r="S19" s="8" t="n"/>
-      <c r="T19" s="9" t="n"/>
-      <c r="U19" s="9" t="n"/>
-      <c r="V19" s="9" t="n"/>
-      <c r="W19" s="8" t="n"/>
-      <c r="X19" s="9" t="n"/>
-      <c r="Y19" s="9" t="n"/>
-      <c r="Z19" s="9" t="n"/>
-      <c r="AA19" s="8" t="n"/>
-      <c r="AB19" s="9" t="n"/>
-      <c r="AC19" s="9" t="n"/>
-      <c r="AD19" s="9" t="n"/>
-      <c r="AE19" s="8" t="n"/>
-      <c r="AF19" s="9" t="n"/>
-      <c r="AG19" s="9" t="n"/>
-      <c r="AH19" s="9" t="n"/>
-      <c r="AI19" s="8" t="n"/>
-      <c r="AJ19" s="9" t="n"/>
-      <c r="AK19" s="9" t="n"/>
-      <c r="AL19" s="9" t="n"/>
-      <c r="AM19" s="8" t="n"/>
-      <c r="AN19" s="9" t="n"/>
-      <c r="AO19" s="9" t="n"/>
-      <c r="AP19" s="9" t="n"/>
-      <c r="AQ19" s="8" t="n"/>
-      <c r="AR19" s="8" t="n"/>
-      <c r="AS19" s="8" t="n"/>
-      <c r="AT19" s="33" t="n"/>
-      <c r="AU19" s="33" t="n"/>
-      <c r="AV19" s="11" t="n"/>
+      <c r="F19" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="G19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL19" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM19" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AN19" s="9" t="n">
+        <v>24</v>
+      </c>
+      <c r="AO19" s="9" t="n">
+        <v>34</v>
+      </c>
+      <c r="AP19" s="9" t="n">
+        <v>23</v>
+      </c>
+      <c r="AQ19" s="8" t="n">
+        <v>24</v>
+      </c>
+      <c r="AR19" s="8" t="n">
+        <v>34</v>
+      </c>
+      <c r="AS19" s="8" t="n">
+        <v>23</v>
+      </c>
+      <c r="AT19" s="33" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AU19" s="33" t="n">
+        <v>0.96</v>
+      </c>
+      <c r="AV19" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="12" t="n"/>
@@ -2183,49 +3473,135 @@
           <t>야간</t>
         </is>
       </c>
-      <c r="F20" s="8" t="n"/>
-      <c r="G20" s="8" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="9" t="n"/>
-      <c r="K20" s="8" t="n"/>
-      <c r="L20" s="9" t="n"/>
-      <c r="M20" s="9" t="n"/>
-      <c r="N20" s="9" t="n"/>
-      <c r="O20" s="8" t="n"/>
-      <c r="P20" s="9" t="n"/>
-      <c r="Q20" s="9" t="n"/>
-      <c r="R20" s="9" t="n"/>
-      <c r="S20" s="8" t="n"/>
-      <c r="T20" s="9" t="n"/>
-      <c r="U20" s="9" t="n"/>
-      <c r="V20" s="9" t="n"/>
-      <c r="W20" s="8" t="n"/>
-      <c r="X20" s="9" t="n"/>
-      <c r="Y20" s="9" t="n"/>
-      <c r="Z20" s="9" t="n"/>
-      <c r="AA20" s="8" t="n"/>
-      <c r="AB20" s="9" t="n"/>
-      <c r="AC20" s="9" t="n"/>
-      <c r="AD20" s="9" t="n"/>
-      <c r="AE20" s="8" t="n"/>
-      <c r="AF20" s="9" t="n"/>
-      <c r="AG20" s="9" t="n"/>
-      <c r="AH20" s="9" t="n"/>
-      <c r="AI20" s="8" t="n"/>
-      <c r="AJ20" s="9" t="n"/>
-      <c r="AK20" s="9" t="n"/>
-      <c r="AL20" s="9" t="n"/>
-      <c r="AM20" s="8" t="n"/>
-      <c r="AN20" s="9" t="n"/>
-      <c r="AO20" s="9" t="n"/>
-      <c r="AP20" s="9" t="n"/>
-      <c r="AQ20" s="8" t="n"/>
-      <c r="AR20" s="8" t="n"/>
-      <c r="AS20" s="8" t="n"/>
-      <c r="AT20" s="10" t="n"/>
-      <c r="AU20" s="10" t="n"/>
-      <c r="AV20" s="11" t="n"/>
+      <c r="F20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP20" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS20" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU20" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV20" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -2253,49 +3629,135 @@
           <t>주간</t>
         </is>
       </c>
-      <c r="F21" s="8" t="n"/>
-      <c r="G21" s="8" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="9" t="n"/>
-      <c r="K21" s="8" t="n"/>
-      <c r="L21" s="9" t="n"/>
-      <c r="M21" s="9" t="n"/>
-      <c r="N21" s="9" t="n"/>
-      <c r="O21" s="8" t="n"/>
-      <c r="P21" s="9" t="n"/>
-      <c r="Q21" s="9" t="n"/>
-      <c r="R21" s="9" t="n"/>
-      <c r="S21" s="8" t="n"/>
-      <c r="T21" s="9" t="n"/>
-      <c r="U21" s="9" t="n"/>
-      <c r="V21" s="9" t="n"/>
-      <c r="W21" s="8" t="n"/>
-      <c r="X21" s="9" t="n"/>
-      <c r="Y21" s="9" t="n"/>
-      <c r="Z21" s="9" t="n"/>
-      <c r="AA21" s="8" t="n"/>
-      <c r="AB21" s="9" t="n"/>
-      <c r="AC21" s="9" t="n"/>
-      <c r="AD21" s="9" t="n"/>
-      <c r="AE21" s="8" t="n"/>
-      <c r="AF21" s="9" t="n"/>
-      <c r="AG21" s="9" t="n"/>
-      <c r="AH21" s="9" t="n"/>
-      <c r="AI21" s="8" t="n"/>
-      <c r="AJ21" s="9" t="n"/>
-      <c r="AK21" s="9" t="n"/>
-      <c r="AL21" s="9" t="n"/>
-      <c r="AM21" s="8" t="n"/>
-      <c r="AN21" s="9" t="n"/>
-      <c r="AO21" s="9" t="n"/>
-      <c r="AP21" s="9" t="n"/>
-      <c r="AQ21" s="8" t="n"/>
-      <c r="AR21" s="8" t="n"/>
-      <c r="AS21" s="8" t="n"/>
-      <c r="AT21" s="33" t="n"/>
-      <c r="AU21" s="33" t="n"/>
-      <c r="AV21" s="11" t="n"/>
+      <c r="F21" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="G21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL21" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM21" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AN21" s="9" t="n">
+        <v>14</v>
+      </c>
+      <c r="AO21" s="9" t="n">
+        <v>30</v>
+      </c>
+      <c r="AP21" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="AQ21" s="8" t="n">
+        <v>14</v>
+      </c>
+      <c r="AR21" s="8" t="n">
+        <v>30</v>
+      </c>
+      <c r="AS21" s="8" t="n">
+        <v>13</v>
+      </c>
+      <c r="AT21" s="33" t="n">
+        <v>2.14</v>
+      </c>
+      <c r="AU21" s="33" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="AV21" s="11" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="12" t="n"/>
@@ -2307,49 +3769,135 @@
           <t>야간</t>
         </is>
       </c>
-      <c r="F22" s="8" t="n"/>
-      <c r="G22" s="8" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="9" t="n"/>
-      <c r="K22" s="8" t="n"/>
-      <c r="L22" s="9" t="n"/>
-      <c r="M22" s="9" t="n"/>
-      <c r="N22" s="9" t="n"/>
-      <c r="O22" s="8" t="n"/>
-      <c r="P22" s="9" t="n"/>
-      <c r="Q22" s="9" t="n"/>
-      <c r="R22" s="9" t="n"/>
-      <c r="S22" s="8" t="n"/>
-      <c r="T22" s="9" t="n"/>
-      <c r="U22" s="9" t="n"/>
-      <c r="V22" s="9" t="n"/>
-      <c r="W22" s="8" t="n"/>
-      <c r="X22" s="9" t="n"/>
-      <c r="Y22" s="9" t="n"/>
-      <c r="Z22" s="9" t="n"/>
-      <c r="AA22" s="8" t="n"/>
-      <c r="AB22" s="9" t="n"/>
-      <c r="AC22" s="9" t="n"/>
-      <c r="AD22" s="9" t="n"/>
-      <c r="AE22" s="8" t="n"/>
-      <c r="AF22" s="9" t="n"/>
-      <c r="AG22" s="9" t="n"/>
-      <c r="AH22" s="9" t="n"/>
-      <c r="AI22" s="8" t="n"/>
-      <c r="AJ22" s="9" t="n"/>
-      <c r="AK22" s="9" t="n"/>
-      <c r="AL22" s="9" t="n"/>
-      <c r="AM22" s="8" t="n"/>
-      <c r="AN22" s="9" t="n"/>
-      <c r="AO22" s="9" t="n"/>
-      <c r="AP22" s="9" t="n"/>
-      <c r="AQ22" s="8" t="n"/>
-      <c r="AR22" s="8" t="n"/>
-      <c r="AS22" s="8" t="n"/>
-      <c r="AT22" s="10" t="n"/>
-      <c r="AU22" s="10" t="n"/>
-      <c r="AV22" s="11" t="n"/>
+      <c r="F22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="H22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="J22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="R22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="S22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="U22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="X22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AC22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AF22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AK22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AL22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AM22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AP22" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AR22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AS22" s="8" t="n">
+        <v>0</v>
+      </c>
+      <c r="AT22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AU22" s="10" t="n">
+        <v>0</v>
+      </c>
+      <c r="AV22" s="11" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="16" t="inlineStr">
@@ -2398,12 +3946,24 @@
       <c r="AN23" s="4" t="n"/>
       <c r="AO23" s="4" t="n"/>
       <c r="AP23" s="4" t="n"/>
-      <c r="AQ23" s="4" t="n"/>
-      <c r="AR23" s="4" t="n"/>
-      <c r="AS23" s="4" t="n"/>
-      <c r="AT23" s="34" t="n"/>
-      <c r="AU23" s="34" t="n"/>
-      <c r="AV23" s="4" t="n"/>
+      <c r="AQ23" s="4" t="n">
+        <v>368</v>
+      </c>
+      <c r="AR23" s="4" t="n">
+        <v>3847</v>
+      </c>
+      <c r="AS23" s="4" t="n">
+        <v>395</v>
+      </c>
+      <c r="AT23" s="34" t="n">
+        <v>10.45</v>
+      </c>
+      <c r="AU23" s="34" t="n">
+        <v>1.07</v>
+      </c>
+      <c r="AV23" s="4" t="n">
+        <v>-27</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="20">
